--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4740" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4740" uniqueCount="754">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:54:27+00:00</t>
+    <t>2026-01-30T10:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,6 +658,9 @@
     <t>Extension créée dans le cadre du ROR pour représenter le code officiel géographique (COG) de la commune dans laquelle le lieu est situé.</t>
   </si>
   <si>
+    <t>CommuneCog</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-equipment</t>
   </si>
   <si>
@@ -675,6 +678,9 @@
  Device représente une instance d'un équipement alors l'équipement pour le ROR correspond juste au nombre d'équipement de même type.</t>
   </si>
   <si>
+    <t>EquipementSpecifique</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-residential-capacity</t>
   </si>
   <si>
@@ -691,6 +697,9 @@
     <t>Extension créée dans le cadre du ROR qui décrit un type d'habitation adapté à la réalisation d'une offre.</t>
   </si>
   <si>
+    <t>CapaciteHabitation</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-supported-capacity</t>
   </si>
   <si>
@@ -707,6 +716,9 @@
     <t>Extension créée dans le cadre du ROR qui indique une série d’enregistrements indiquant la quantité de lit (ou de place) de l'entité pour un statut et une temporalité donnés.</t>
   </si>
   <si>
+    <t>CapacitePriseCharge</t>
+  </si>
+  <si>
     <t>Location.extension:ror-meta-creation-date</t>
   </si>
   <si>
@@ -1506,7 +1518,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>adresseTelecom</t>
+    <t>telecommunication.adresseTelecom</t>
   </si>
   <si>
     <t>./url</t>
@@ -4796,7 +4808,7 @@
         <v>118</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -4807,13 +4819,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>75</v>
@@ -4835,13 +4847,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4907,7 +4919,7 @@
         <v>118</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4918,13 +4930,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>75</v>
@@ -4946,13 +4958,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5018,7 +5030,7 @@
         <v>118</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>75</v>
@@ -5029,13 +5041,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>75</v>
@@ -5057,13 +5069,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5129,7 +5141,7 @@
         <v>118</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>75</v>
@@ -5140,13 +5152,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -5168,13 +5180,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5251,13 +5263,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -5279,13 +5291,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5362,10 +5374,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5391,16 +5403,16 @@
         <v>110</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -5449,7 +5461,7 @@
         <v>116</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5475,10 +5487,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5501,17 +5513,17 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -5548,7 +5560,7 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5558,7 +5570,7 @@
         <v>116</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5576,21 +5588,21 @@
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>75</v>
@@ -5612,17 +5624,17 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -5671,7 +5683,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5686,21 +5698,21 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5806,10 +5818,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5917,10 +5929,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5946,16 +5958,16 @@
         <v>173</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5983,10 +5995,10 @@
         <v>164</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -6004,7 +6016,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -6022,7 +6034,7 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>75</v>
@@ -6030,10 +6042,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6056,19 +6068,19 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -6096,10 +6108,10 @@
         <v>148</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -6117,7 +6129,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -6135,7 +6147,7 @@
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>75</v>
@@ -6143,10 +6155,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6252,10 +6264,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6363,10 +6375,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6392,16 +6404,16 @@
         <v>144</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -6450,7 +6462,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6468,7 +6480,7 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>75</v>
@@ -6476,10 +6488,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6585,10 +6597,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6696,10 +6708,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6725,16 +6737,16 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -6783,7 +6795,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6801,7 +6813,7 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -6809,10 +6821,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6838,13 +6850,13 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6894,7 +6906,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6912,7 +6924,7 @@
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>75</v>
@@ -6920,10 +6932,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6949,16 +6961,16 @@
         <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6968,7 +6980,7 @@
         <v>75</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>75</v>
@@ -7007,7 +7019,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -7025,7 +7037,7 @@
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
@@ -7033,10 +7045,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7062,16 +7074,16 @@
         <v>103</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -7120,7 +7132,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -7138,7 +7150,7 @@
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -7146,10 +7158,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7172,19 +7184,19 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -7233,7 +7245,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7251,7 +7263,7 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -7259,10 +7271,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7288,16 +7300,16 @@
         <v>103</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -7346,7 +7358,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7364,7 +7376,7 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -7372,10 +7384,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7401,16 +7413,16 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -7423,7 +7435,7 @@
         <v>75</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>75</v>
@@ -7459,7 +7471,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7477,7 +7489,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -7485,10 +7497,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7514,13 +7526,13 @@
         <v>103</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7534,7 +7546,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -7570,7 +7582,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7588,7 +7600,7 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -7596,10 +7608,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7622,16 +7634,16 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7681,7 +7693,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7693,13 +7705,13 @@
         <v>98</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -7707,10 +7719,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7733,16 +7745,16 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7792,7 +7804,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7804,13 +7816,13 @@
         <v>98</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
@@ -7818,13 +7830,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -7846,17 +7858,17 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7905,7 +7917,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7920,21 +7932,21 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8040,10 +8052,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8151,10 +8163,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8180,16 +8192,16 @@
         <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -8217,10 +8229,10 @@
         <v>164</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -8238,7 +8250,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8256,7 +8268,7 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
@@ -8264,10 +8276,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8290,19 +8302,19 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -8330,10 +8342,10 @@
         <v>148</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -8351,7 +8363,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8369,7 +8381,7 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>75</v>
@@ -8377,10 +8389,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8486,10 +8498,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8597,10 +8609,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8626,16 +8638,16 @@
         <v>144</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8684,7 +8696,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8702,7 +8714,7 @@
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>75</v>
@@ -8710,10 +8722,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8819,10 +8831,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8930,10 +8942,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8959,16 +8971,16 @@
         <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -9017,7 +9029,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9035,7 +9047,7 @@
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>75</v>
@@ -9043,10 +9055,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9072,13 +9084,13 @@
         <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9128,7 +9140,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -9146,7 +9158,7 @@
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>75</v>
@@ -9154,10 +9166,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9183,16 +9195,16 @@
         <v>173</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -9202,7 +9214,7 @@
         <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>75</v>
@@ -9241,7 +9253,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9259,7 +9271,7 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>75</v>
@@ -9267,10 +9279,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9296,16 +9308,16 @@
         <v>103</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -9354,7 +9366,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9372,7 +9384,7 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>75</v>
@@ -9380,10 +9392,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9406,19 +9418,19 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -9467,7 +9479,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9485,7 +9497,7 @@
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>75</v>
@@ -9493,10 +9505,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9522,16 +9534,16 @@
         <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -9580,7 +9592,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9598,7 +9610,7 @@
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -9606,10 +9618,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9635,16 +9647,16 @@
         <v>132</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -9657,7 +9669,7 @@
         <v>75</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>75</v>
@@ -9693,7 +9705,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9711,7 +9723,7 @@
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
@@ -9719,10 +9731,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9748,13 +9760,13 @@
         <v>103</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9768,7 +9780,7 @@
         <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>75</v>
@@ -9804,7 +9816,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9822,7 +9834,7 @@
         <v>75</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -9830,10 +9842,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9856,16 +9868,16 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9915,7 +9927,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9927,13 +9939,13 @@
         <v>98</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
@@ -9941,10 +9953,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9967,16 +9979,16 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10026,7 +10038,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10038,13 +10050,13 @@
         <v>98</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
@@ -10052,10 +10064,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10081,13 +10093,13 @@
         <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10116,28 +10128,28 @@
         <v>164</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Z67" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10152,21 +10164,21 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10192,13 +10204,13 @@
         <v>144</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10228,25 +10240,25 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10261,21 +10273,21 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>152</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10301,13 +10313,13 @@
         <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10357,7 +10369,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10372,10 +10384,10 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>75</v>
@@ -10383,10 +10395,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10412,16 +10424,16 @@
         <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -10461,7 +10473,7 @@
         <v>114</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>75</v>
@@ -10470,7 +10482,7 @@
         <v>116</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10488,7 +10500,7 @@
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>75</v>
@@ -10496,13 +10508,13 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>75</v>
@@ -10527,16 +10539,16 @@
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10585,7 +10597,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10600,10 +10612,10 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>75</v>
@@ -10611,10 +10623,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10640,16 +10652,16 @@
         <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10698,7 +10710,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10713,10 +10725,10 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>75</v>
@@ -10724,10 +10736,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10753,16 +10765,16 @@
         <v>173</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10790,10 +10802,10 @@
         <v>164</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10811,7 +10823,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10829,18 +10841,18 @@
         <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10863,16 +10875,16 @@
         <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10902,25 +10914,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10935,21 +10947,21 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10972,13 +10984,13 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11029,7 +11041,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11041,13 +11053,13 @@
         <v>98</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>75</v>
@@ -11055,10 +11067,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11164,10 +11176,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11273,13 +11285,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>75</v>
@@ -11301,13 +11313,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11384,13 +11396,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>75</v>
@@ -11412,13 +11424,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11495,13 +11507,13 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>75</v>
@@ -11523,13 +11535,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11606,10 +11618,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11635,13 +11647,13 @@
         <v>173</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11670,10 +11682,10 @@
         <v>164</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>75</v>
@@ -11691,7 +11703,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11700,7 +11712,7 @@
         <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>99</v>
@@ -11709,7 +11721,7 @@
         <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>75</v>
@@ -11717,10 +11729,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11746,16 +11758,16 @@
         <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -11804,7 +11816,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11819,10 +11831,10 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>75</v>
@@ -11830,10 +11842,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11859,16 +11871,16 @@
         <v>173</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11896,10 +11908,10 @@
         <v>164</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>75</v>
@@ -11917,7 +11929,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11935,7 +11947,7 @@
         <v>75</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>75</v>
@@ -11943,10 +11955,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11969,16 +11981,16 @@
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12028,7 +12040,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12054,10 +12066,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12080,16 +12092,16 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12139,7 +12151,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12151,13 +12163,13 @@
         <v>98</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
@@ -12165,10 +12177,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12191,19 +12203,19 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -12252,7 +12264,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12267,10 +12279,10 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
@@ -12278,10 +12290,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12387,10 +12399,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12498,10 +12510,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12527,16 +12539,16 @@
         <v>173</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -12549,7 +12561,7 @@
         <v>75</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>75</v>
@@ -12564,10 +12576,10 @@
         <v>164</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -12585,7 +12597,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12603,7 +12615,7 @@
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -12611,10 +12623,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12640,13 +12652,13 @@
         <v>173</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12660,7 +12672,7 @@
         <v>75</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>75</v>
@@ -12675,10 +12687,10 @@
         <v>164</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -12696,7 +12708,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12714,7 +12726,7 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>75</v>
@@ -12722,10 +12734,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12751,16 +12763,16 @@
         <v>103</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12773,7 +12785,7 @@
         <v>75</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>75</v>
@@ -12809,7 +12821,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12827,7 +12839,7 @@
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>75</v>
@@ -12835,10 +12847,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12864,13 +12876,13 @@
         <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12884,7 +12896,7 @@
         <v>75</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>75</v>
@@ -12920,7 +12932,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12938,7 +12950,7 @@
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>75</v>
@@ -12946,10 +12958,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13055,10 +13067,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13166,13 +13178,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>75</v>
@@ -13194,13 +13206,13 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13266,10 +13278,10 @@
         <v>118</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>75</v>
@@ -13277,13 +13289,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>75</v>
@@ -13305,13 +13317,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13377,10 +13389,10 @@
         <v>118</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>75</v>
@@ -13388,13 +13400,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>75</v>
@@ -13416,13 +13428,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13488,10 +13500,10 @@
         <v>118</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>75</v>
@@ -13499,13 +13511,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>75</v>
@@ -13527,13 +13539,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13599,10 +13611,10 @@
         <v>118</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>75</v>
@@ -13610,13 +13622,13 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>75</v>
@@ -13638,13 +13650,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13710,10 +13722,10 @@
         <v>118</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>75</v>
@@ -13721,10 +13733,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13830,10 +13842,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13939,10 +13951,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13968,13 +13980,13 @@
         <v>132</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13982,7 +13994,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>75</v>
@@ -14024,7 +14036,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>85</v>
@@ -14050,10 +14062,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14079,10 +14091,10 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14113,7 +14125,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>75</v>
@@ -14131,7 +14143,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -14140,7 +14152,7 @@
         <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14157,13 +14169,13 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>75</v>
@@ -14185,13 +14197,13 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14257,10 +14269,10 @@
         <v>118</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>75</v>
@@ -14268,13 +14280,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -14296,13 +14308,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14368,10 +14380,10 @@
         <v>118</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>75</v>
@@ -14379,13 +14391,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>75</v>
@@ -14407,13 +14419,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14479,7 +14491,7 @@
         <v>118</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>75</v>
@@ -14490,10 +14502,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14519,10 +14531,10 @@
         <v>103</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14546,7 +14558,7 @@
         <v>75</v>
       </c>
       <c r="W107" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="X107" t="s" s="2">
         <v>75</v>
@@ -14573,7 +14585,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14599,14 +14611,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14628,13 +14640,13 @@
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14648,7 +14660,7 @@
         <v>75</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>75</v>
@@ -14684,7 +14696,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14699,10 +14711,10 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>75</v>
@@ -14710,14 +14722,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14739,13 +14751,13 @@
         <v>103</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14759,7 +14771,7 @@
         <v>75</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>75</v>
@@ -14795,7 +14807,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14813,7 +14825,7 @@
         <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>75</v>
@@ -14821,14 +14833,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14850,13 +14862,13 @@
         <v>103</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14906,7 +14918,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14924,7 +14936,7 @@
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14932,14 +14944,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14961,13 +14973,13 @@
         <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14981,7 +14993,7 @@
         <v>75</v>
       </c>
       <c r="T111" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="U111" t="s" s="2">
         <v>75</v>
@@ -15017,7 +15029,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15032,10 +15044,10 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>75</v>
@@ -15043,10 +15055,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15072,13 +15084,13 @@
         <v>103</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15128,7 +15140,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15146,7 +15158,7 @@
         <v>75</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>75</v>
@@ -15154,10 +15166,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15180,19 +15192,19 @@
         <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -15205,7 +15217,7 @@
         <v>75</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>75</v>
@@ -15241,7 +15253,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15253,13 +15265,13 @@
         <v>98</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>75</v>
@@ -15267,10 +15279,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15293,19 +15305,19 @@
         <v>86</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15333,28 +15345,28 @@
         <v>157</v>
       </c>
       <c r="Y114" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF114" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15372,18 +15384,18 @@
         <v>75</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15406,17 +15418,17 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -15465,7 +15477,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15480,10 +15492,10 @@
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>75</v>
@@ -15491,10 +15503,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15600,10 +15612,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15711,13 +15723,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>75</v>
@@ -15739,13 +15751,13 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -15822,14 +15834,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15851,16 +15863,16 @@
         <v>110</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -15909,7 +15921,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15935,10 +15947,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15961,16 +15973,16 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16020,7 +16032,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>85</v>
@@ -16035,10 +16047,10 @@
         <v>99</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>75</v>
@@ -16046,10 +16058,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16072,16 +16084,16 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16131,7 +16143,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>85</v>
@@ -16146,10 +16158,10 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>75</v>
@@ -16157,10 +16169,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16183,16 +16195,16 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16242,7 +16254,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16260,7 +16272,7 @@
         <v>75</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>75</v>
@@ -16268,10 +16280,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16294,19 +16306,19 @@
         <v>86</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -16355,7 +16367,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16367,13 +16379,13 @@
         <v>98</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>75</v>
@@ -16381,10 +16393,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16407,19 +16419,19 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -16468,7 +16480,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16480,13 +16492,13 @@
         <v>98</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>75</v>
@@ -16494,10 +16506,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16520,16 +16532,16 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16579,7 +16591,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16597,7 +16609,7 @@
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>75</v>
@@ -16605,10 +16617,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16714,10 +16726,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16825,14 +16837,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16854,16 +16866,16 @@
         <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -16912,7 +16924,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16938,10 +16950,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16967,13 +16979,13 @@
         <v>173</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17002,28 +17014,28 @@
         <v>164</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="Z129" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17041,7 +17053,7 @@
         <v>75</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>75</v>
@@ -17049,10 +17061,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17075,13 +17087,13 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17132,7 +17144,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17150,7 +17162,7 @@
         <v>75</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>75</v>
@@ -17158,10 +17170,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17184,13 +17196,13 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17241,7 +17253,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17259,7 +17271,7 @@
         <v>75</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>75</v>
@@ -17267,10 +17279,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17293,13 +17305,13 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17350,7 +17362,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17368,7 +17380,7 @@
         <v>75</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>75</v>
@@ -17376,10 +17388,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17405,13 +17417,13 @@
         <v>103</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17461,7 +17473,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17487,10 +17499,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17513,19 +17525,19 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -17574,7 +17586,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17586,13 +17598,13 @@
         <v>98</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>Location.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour gérer le code région définissant la région source des données</t>
@@ -572,7 +572,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -891,7 +891,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1177,7 +1177,7 @@
     <t>Location.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -2122,7 +2122,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -2359,7 +2359,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -2690,17 +2690,17 @@
   <dimension ref="A1:AM135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.4296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.98046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="40.8828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.80859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.84765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="35.05078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="138.9140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="119.09375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2709,25 +2709,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="86.125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="78.25390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.31640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.8359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.2734375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="67.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.84765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="51.49609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="44.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3509,7 +3509,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>201</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>219</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>225</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>237</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>255</v>
       </c>
@@ -6173,7 +6173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>272</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>381</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>388</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>413</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>419</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>431</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>433</v>
       </c>
@@ -10980,7 +10980,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>447</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>454</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>463</v>
       </c>
@@ -11527,7 +11527,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>468</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>473</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>486</v>
       </c>
@@ -13309,7 +13309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>557</v>
       </c>
@@ -13420,7 +13420,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>564</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>571</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>578</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>585</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>610</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>617</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>624</v>
       </c>
@@ -15854,7 +15854,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>691</v>
       </c>
@@ -16411,7 +16411,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>715</v>
       </c>
@@ -16524,7 +16524,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>722</v>
       </c>
@@ -17745,12 +17745,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM135">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-location.xlsx
+++ b/main/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
